--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-12-2025.xlsx
@@ -592,25 +592,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -712,25 +712,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -832,25 +832,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -952,25 +952,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -1072,25 +1072,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -1192,25 +1192,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -1312,25 +1312,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -1432,25 +1432,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -1552,25 +1552,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -1672,25 +1672,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -1792,25 +1792,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -1912,25 +1912,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -2032,25 +2032,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -2152,25 +2152,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -2272,25 +2272,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -2489,25 +2489,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -2609,25 +2609,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -2729,25 +2729,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -2849,25 +2849,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -2969,25 +2969,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -3089,25 +3089,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -3209,25 +3209,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -3329,25 +3329,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
@@ -3449,25 +3449,25 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6a3718255
-	0x7ff6a37182b0
-	0x7ff6a34f165d
-	0x7ff6a3549a33
-	0x7ff6a3549d3c
-	0x7ff6a359df67
-	0x7ff6a359ac97
-	0x7ff6a353ac29
-	0x7ff6a353ba93
-	0x7ff6a3a2fff0
-	0x7ff6a3a2a930
-	0x7ff6a3a49096
-	0x7ff6a3735754
-	0x7ff6a373e6fc
-	0x7ff6a3721974
-	0x7ff6a3721b25
-	0x7ff6a3707852
-	0x7ffeb4f2e8d7
-	0x7ffeb602c53c
+	0x7ff7d90c8255
+	0x7ff7d90c82b0
+	0x7ff7d8ea165d
+	0x7ff7d8ef9a33
+	0x7ff7d8ef9d3c
+	0x7ff7d8f4df67
+	0x7ff7d8f4ac97
+	0x7ff7d8eeac29
+	0x7ff7d8eeba93
+	0x7ff7d93dfff0
+	0x7ff7d93da930
+	0x7ff7d93f9096
+	0x7ff7d90e5754
+	0x7ff7d90ee6fc
+	0x7ff7d90d1974
+	0x7ff7d90d1b25
+	0x7ff7d90b7852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
 </t>
         </is>
       </c>
